--- a/public/assets/data/resume.xlsx
+++ b/public/assets/data/resume.xlsx
@@ -1,44 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\portfolio\public\assets\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA4E9B-8944-4313-B906-AF4F39F574C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Experience" sheetId="1" r:id="rId1"/>
     <sheet name="Education" sheetId="2" r:id="rId2"/>
     <sheet name="Skills" sheetId="3" r:id="rId3"/>
     <sheet name="Bio" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>achievements</t>
+  </si>
+  <si>
+    <t>Software Development Intern</t>
+  </si>
+  <si>
+    <t>Safe Lanes</t>
+  </si>
+  <si>
+    <t>Jul 2025 – Aug 2025</t>
+  </si>
+  <si>
+    <t>Worked on frontend and backend solutions including UI components, secure file handling, and AI chatbots.</t>
+  </si>
+  <si>
+    <t>Built a Windows 11–style notification drawer with real-time updates and category filters | Developed a secure PDF viewer with password protection and anti-copy/print features | Created a Retrieval-Augmented Generation chatbot using HuggingFace, FAISS, and Streamlit</t>
+  </si>
+  <si>
+    <t>Student Body Captain</t>
+  </si>
+  <si>
+    <t>Fahaheel Al Watanieh Indian Private School (DPS Kuwait)</t>
+  </si>
+  <si>
+    <t>Sep 2023 – Feb 2024</t>
+  </si>
+  <si>
+    <t>Led student activities, competitions, and discipline management across the school community.</t>
+  </si>
+  <si>
+    <t>Organized and led 4 interhouse competitions, boosting student participation by 50% | Reduced disciplinary incidents by 40% through peer mentorship | Secured 5 wins in interhouse events, increasing house points by 70%</t>
+  </si>
+  <si>
+    <t>Director of Graphic Design</t>
+  </si>
+  <si>
+    <t>Aug 2023 – Oct 2023</t>
+  </si>
+  <si>
+    <t>Directed the design of school magazines and coordinated with editorial teams.</t>
+  </si>
+  <si>
+    <t>Designed 4 magazine covers and 6 sub-covers with cohesive visual themes | Contributed to a 30% increase in distribution and 50% rise in reader engagement | Achieved 90% satisfaction from editorial staff for design quality</t>
+  </si>
+  <si>
+    <t>Director of Computer Science</t>
+  </si>
+  <si>
+    <t>Sep 2022 – Mar 2023</t>
+  </si>
+  <si>
+    <t>Founded and led the Computer Science Club, organizing events and mentoring peers.</t>
+  </si>
+  <si>
+    <t>Grew club membership by 70% and boosted student proficiency in MS Office by 60% | Organized 3 computer science events and 4 creative contests | Secured 2 interschool competition victories for the school</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>Contract Role</t>
+  </si>
+  <si>
+    <t>Dec 2022</t>
+  </si>
+  <si>
+    <t>Designed visuals for a school event to ensure aesthetic appeal and branding.</t>
+  </si>
+  <si>
+    <t>Produced 5 high-quality graphic visuals for event backdrops | Improved efficiency by reducing design revisions by 30% | Contributed to 40% increase in attendee engagement</t>
+  </si>
+  <si>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>Freelance</t>
+  </si>
+  <si>
+    <t>Feb 2022 – May 2022</t>
+  </si>
+  <si>
+    <t>Organized large-scale events with responsibility for planning, marketing, and budgeting.</t>
+  </si>
+  <si>
+    <t>Executed 5+ events with 150+ attendees each | Increased attendance by 30% and revenue by 20% | Managed budgets of ₹50,000 per event while balancing academic commitments</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>BSc.Honors in Computer Science with Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>University Of Alberta</t>
+  </si>
+  <si>
+    <t>2024 - 2028</t>
+  </si>
+  <si>
+    <t>Pursuing a degree in Computer Science with a concentration in Artificial Intelligence. Coursework includes software engineering, machine learning, data structures, and web development, with practical experience through projects and research.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>React</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>Streamlit</t>
+  </si>
+  <si>
+    <t>Tailwind CSS</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Node.js</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+  </si>
+  <si>
+    <t>MongoDB</t>
+  </si>
+  <si>
+    <t>Tools &amp; Automation</t>
+  </si>
+  <si>
+    <t>Git</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>N8N</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>highlights</t>
+  </si>
+  <si>
+    <t>Raghav Sethi</t>
+  </si>
+  <si>
+    <t>App Developer &amp; AI Enthusiast</t>
+  </si>
+  <si>
+    <t>Welcome to my digital workspace. I’m a developer who enjoys working with web technologies and artificial intelligence. I focus on building practical, user-friendly solutions and am always looking for ways to learn and improve through my projects.</t>
+  </si>
+  <si>
+    <t>Python, N8N, React, AI/ML, Angular, SQL</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -68,13 +248,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -399,363 +587,378 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="92.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="232.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>title</v>
-      </c>
-      <c r="B1" t="str">
-        <v>company</v>
-      </c>
-      <c r="C1" t="str">
-        <v>period</v>
-      </c>
-      <c r="D1" t="str">
-        <v>description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>achievements</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Software Development Intern</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Safe Lanes</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Jul 2025 – Aug 2025</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Worked on frontend and backend solutions including UI components, secure file handling, and AI chatbots.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Built a Windows 11–style notification drawer with real-time updates and category filters | Developed a secure PDF viewer with password protection and anti-copy/print features | Created a Retrieval-Augmented Generation chatbot using HuggingFace, FAISS, and Streamlit</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Student Body Captain</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Fahaheel Al Watanieh Indian Private School (DPS Kuwait)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Sep 2023 – Feb 2024</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Led student activities, competitions, and discipline management across the school community.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Organized and led 4 interhouse competitions, boosting student participation by 50% | Reduced disciplinary incidents by 40% through peer mentorship | Secured 5 wins in interhouse events, increasing house points by 70%</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Director of Graphic Design</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Fahaheel Al Watanieh Indian Private School (DPS Kuwait)</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Aug 2023 – Oct 2023</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Directed the design of school magazines and coordinated with editorial teams.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Designed 4 magazine covers and 6 sub-covers with cohesive visual themes | Contributed to a 30% increase in distribution and 50% rise in reader engagement | Achieved 90% satisfaction from editorial staff for design quality</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Director of Computer Science</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Fahaheel Al Watanieh Indian Private School (DPS Kuwait)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Sep 2022 – Mar 2023</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Founded and led the Computer Science Club, organizing events and mentoring peers.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Grew club membership by 70% and boosted student proficiency in MS Office by 60% | Organized 3 computer science events and 4 creative contests | Secured 2 interschool competition victories for the school</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Graphic Designer</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Contract Role</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Dec 2022</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Designed visuals for a school event to ensure aesthetic appeal and branding.</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Produced 5 high-quality graphic visuals for event backdrops | Improved efficiency by reducing design revisions by 30% | Contributed to 40% increase in attendee engagement</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Event Manager</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Freelance</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Feb 2022 – May 2022</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Organized large-scale events with responsibility for planning, marketing, and budgeting.</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Executed 5+ events with 150+ attendees each | Increased attendance by 30% and revenue by 20% | Managed budgets of ₹50,000 per event while balancing academic commitments</v>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError sqref="A1:E7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>degree</v>
-      </c>
-      <c r="B1" t="str">
-        <v>school</v>
-      </c>
-      <c r="C1" t="str">
-        <v>period</v>
-      </c>
-      <c r="D1" t="str">
-        <v>description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>BSc.Honors in Computer Science with Artificial Intelligence</v>
-      </c>
-      <c r="B2" t="str">
-        <v>University Of Alberta</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2024 - 2028</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pursuing a degree in Computer Science with a concentration in Artificial Intelligence. Coursework includes software engineering, machine learning, data structures, and web development, with practical experience through projects and research.</v>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError sqref="A1:D2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Skill</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Level</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Frontend</v>
-      </c>
-      <c r="B2" t="str">
-        <v>React</v>
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
       </c>
       <c r="C2">
         <v>95</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Frontend</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Angular</v>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
       </c>
       <c r="C3">
         <v>85</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Frontend</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Streamlit</v>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
       </c>
       <c r="C4">
         <v>90</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Frontend</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tailwind CSS</v>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
       </c>
       <c r="C5">
         <v>88</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Backend</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Node.js</v>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
       </c>
       <c r="C6">
         <v>92</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Backend</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Python</v>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
       </c>
       <c r="C7">
         <v>88</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Backend</v>
-      </c>
-      <c r="B8" t="str">
-        <v>PostgreSQL</v>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
       </c>
       <c r="C8">
         <v>85</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Backend</v>
-      </c>
-      <c r="B9" t="str">
-        <v>MongoDB</v>
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
       </c>
       <c r="C9">
         <v>80</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Tools &amp; Automation</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Git</v>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
       </c>
       <c r="C10">
         <v>95</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Tools &amp; Automation</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Docker</v>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
       </c>
       <c r="C11">
         <v>82</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Tools &amp; Automation</v>
-      </c>
-      <c r="B12" t="str">
-        <v>N8N</v>
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
       </c>
       <c r="C12">
         <v>78</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Tools &amp; Automation</v>
-      </c>
-      <c r="B13" t="str">
-        <v>AWS</v>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
       </c>
       <c r="C13">
         <v>75</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError sqref="A1:C13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>title</v>
-      </c>
-      <c r="C1" t="str">
-        <v>description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>highlights</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Raghav Sethi</v>
-      </c>
-      <c r="B2" t="str">
-        <v>App Developer &amp; AI Enthusiast</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Welcome to my digital workspace. I’m a developer who enjoys working with web technologies and artificial intelligence. I focus on building practical, user-friendly solutions and am always looking for ways to learn and improve through my projects.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Python, N8N, React, AI/ML, Angular, SQL</v>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError sqref="A1:D2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/data/resume.xlsx
+++ b/public/assets/data/resume.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\portfolio\public\assets\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\My Projects\portfolio\public\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EA4E9B-8944-4313-B906-AF4F39F574C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2D48FE-483D-4C8F-9FD5-E123568534FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>title</t>
   </si>
@@ -199,9 +199,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>highlights</t>
-  </si>
-  <si>
     <t>Raghav Sethi</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
   </si>
   <si>
     <t>Welcome to my digital workspace. I’m a developer who enjoys working with web technologies and artificial intelligence. I focus on building practical, user-friendly solutions and am always looking for ways to learn and improve through my projects.</t>
-  </si>
-  <si>
-    <t>Python, N8N, React, AI/ML, Angular, SQL</t>
   </si>
 </sst>
 </file>
@@ -589,7 +583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.3984375" bestFit="1" customWidth="1"/>
@@ -598,7 +592,7 @@
     <col min="5" max="5" width="232.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -632,7 +626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -649,7 +643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -666,7 +660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -683,7 +677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -700,7 +694,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -728,9 +722,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="50.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="209.19921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -744,7 +744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -769,9 +769,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="28.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -782,7 +786,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -793,7 +797,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -804,7 +808,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -815,7 +819,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -826,7 +830,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -837,7 +841,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -848,7 +852,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -859,7 +863,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -870,7 +874,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -881,7 +885,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -892,7 +896,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -903,7 +907,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -925,9 +929,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.69921875" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="4" width="96.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -938,27 +947,27 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>